--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2021_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2021_los_rios.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:39</t>
+    <t xml:space="preserve">2026-09-09 20:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2021_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2021_los_rios.xlsx
@@ -24,39 +24,39 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Valdivia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Corral</t>
   </si>
   <si>
+    <t xml:space="preserve">Lanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariquina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paillaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panguipulli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Unión</t>
+  </si>
+  <si>
     <t xml:space="preserve">Futrono</t>
   </si>
   <si>
-    <t xml:space="preserve">La Unión</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lago Ranco</t>
   </si>
   <si>
-    <t xml:space="preserve">Lanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Lagos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Máfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariquina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paillaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panguipulli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valdivia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:43</t>
+    <t xml:space="preserve">2026-09-18 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -478,7 +478,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>77.41</v>
+        <v>77.38</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>71.79</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>77.84</v>
+        <v>76.96</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>73.29</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="6">
@@ -510,7 +510,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>76.96</v>
+        <v>77.06</v>
       </c>
     </row>
     <row r="7">
@@ -518,7 +518,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>73.75</v>
+        <v>75.64</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +526,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>77.06</v>
+        <v>76.66</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>75.64</v>
+        <v>73.09</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>76.66</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="11">
@@ -550,7 +550,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>73.09</v>
+        <v>71.79</v>
       </c>
     </row>
     <row r="12">
@@ -558,7 +558,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>77.38</v>
+        <v>73.29</v>
       </c>
     </row>
   </sheetData>
